--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -466,13 +466,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.107893960843443</v>
+        <v>0.1488078496738692</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3109932040231828</v>
+        <v>0.1777090734012195</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.4795569668919986</v>
+        <v>0.8870702444028697</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6889579703999503</v>
+        <v>1.307450274914003</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1908290592254748</v>
+        <v>0.08801699435797039</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.6432714806047952</v>
+        <v>1.928274439688923</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>48.35543962708193</v>
+        <v>20.18162877767375</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3942847277129086</v>
+        <v>-0.004234081730814965</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2770565112728391</v>
+        <v>0.3017401763785523</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.797739145234309</v>
+        <v>0.08605335362156492</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.312974346348127</v>
+        <v>0.1253757789236926</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4262120946748346</v>
+        <v>0.1856378394712627</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9542293464547243</v>
+        <v>-0.0237487010607368</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>55.77604875466641</v>
+        <v>40.47565212960476</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.07531924360292863</v>
+        <v>-0.07740705881082244</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2395083322559286</v>
+        <v>0.237835859202895</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.3728766305730928</v>
+        <v>-0.2966047918847033</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.5486737277911464</v>
+        <v>-0.4096729623674741</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2172195637000043</v>
+        <v>0.1858898822152573</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.3616194952846407</v>
+        <v>-0.4329093485019569</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>55.14762178810209</v>
+        <v>48.73015216029906</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1195269603112208</v>
+        <v>0.3440742448647263</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2695440464285593</v>
+        <v>0.3671535669486058</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5125403221267961</v>
+        <v>0.9799506708587289</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.885578076020762</v>
+        <v>1.531261006793622</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.152128540678543</v>
+        <v>0.1675895279193339</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.8201115255407182</v>
+        <v>2.151677134884967</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>58.22812877718462</v>
+        <v>53.75804375318</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2310188636408639</v>
+        <v>0.4894352134591573</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2577082996684975</v>
+        <v>0.2831704299569585</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.9079984905913419</v>
+        <v>1.549389797499819</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.280371057695139</v>
+        <v>2.27345518862533</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1814607842169947</v>
+        <v>0.1926789719658195</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.325529592164026</v>
+        <v>2.655066244660852</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>59.81726560805942</v>
+        <v>65.58756988919757</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.2606133318792891</v>
+        <v>0.7800124645599884</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3208365156687166</v>
+        <v>0.4105381109831818</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.422759420384404</v>
+        <v>2.71813527234568</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.134305123936382</v>
+        <v>4.549386300970895</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.159809897536954</v>
+        <v>0.116626707884101</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.264961301576524</v>
+        <v>15.81532858540935</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>49.41333399998014</v>
+        <v>41.54024612695449</v>
       </c>
     </row>
   </sheetData>
